--- a/artfynd/A 48741-2025 artfynd.xlsx
+++ b/artfynd/A 48741-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>67581061</v>
       </c>
       <c r="B2" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577265.2036601244</v>
+        <v>577265</v>
       </c>
       <c r="R2" t="n">
-        <v>7208294.953727824</v>
+        <v>7208295</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2017-08-19</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2017-08-19</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -817,12 +802,7 @@
         <v>67581063</v>
       </c>
       <c r="B3" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -854,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577399.9256353294</v>
+        <v>577400</v>
       </c>
       <c r="R3" t="n">
-        <v>7208314.962317407</v>
+        <v>7208315</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,19 +867,9 @@
           <t>2017-08-19</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2017-08-19</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
